--- a/data/trans_dic/P32E$bar_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,22; 87,37</t>
+          <t>47,0; 86,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 100,0</t>
+          <t>47,79; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,21; 87,67</t>
+          <t>54,48; 88,44</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,55; 77,96</t>
+          <t>25,05; 75,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,91; 92,23</t>
+          <t>54,5; 94,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,43; 78,85</t>
+          <t>44,71; 80,27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,18; 91,23</t>
+          <t>62,08; 91,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,7; 88,95</t>
+          <t>59,69; 89,15</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,29; 83,4</t>
+          <t>52,95; 83,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,77; 94,91</t>
+          <t>48,15; 94,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,31; 83,27</t>
+          <t>56,09; 83,31</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 74,09</t>
+          <t>35,66; 76,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,88; 85,84</t>
+          <t>28,99; 85,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,96; 73,57</t>
+          <t>40,47; 73,13</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,29; 100,0</t>
+          <t>46,1; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,41; 94,28</t>
+          <t>44,1; 93,99</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,42; 74,47</t>
+          <t>56,94; 74,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65,5; 86,32</t>
+          <t>66,64; 86,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,83; 76,12</t>
+          <t>62,71; 76,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8683; 16776</t>
+          <t>9025; 16542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2978; 6228</t>
+          <t>2976; 6228</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14040; 22292</t>
+          <t>13854; 22488</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3758; 10635</t>
+          <t>3417; 10366</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6034; 10722</t>
+          <t>6336; 11006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10973; 19922</t>
+          <t>11297; 20283</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17624; 26719</t>
+          <t>18182; 26865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19427; 28006</t>
+          <t>18792; 28068</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19835; 32248</t>
+          <t>20476; 32310</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5495; 10075</t>
+          <t>5111; 10023</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28737; 41037</t>
+          <t>27645; 41061</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11904; 24506</t>
+          <t>11796; 25142</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2660; 6943</t>
+          <t>2345; 6950</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16860; 30287</t>
+          <t>16657; 30104</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5588; 12072</t>
+          <t>5565; 12072</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8869; 17639</t>
+          <t>8251; 17585</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80679; 104633</t>
+          <t>80012; 104592</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33292; 43872</t>
+          <t>33872; 43767</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118311; 145646</t>
+          <t>119980; 146072</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$bar_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47,0; 86,15</t>
+          <t>47,26; 87,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,79; 100,0</t>
+          <t>42,92; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,48; 88,44</t>
+          <t>52,46; 87,05</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,05; 75,99</t>
+          <t>25,25; 75,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,5; 94,68</t>
+          <t>47,53; 90,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,71; 80,27</t>
+          <t>41,74; 77,23</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,08; 91,73</t>
+          <t>60,82; 90,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>15,22; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,69; 89,15</t>
+          <t>61,05; 89,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,95; 83,56</t>
+          <t>53,04; 82,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,15; 94,42</t>
+          <t>54,93; 94,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,09; 83,31</t>
+          <t>58,35; 82,98</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,66; 76,01</t>
+          <t>35,67; 74,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,99; 85,92</t>
+          <t>31,6; 85,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,47; 73,13</t>
+          <t>41,49; 73,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,1; 100,0</t>
+          <t>42,91; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,1; 93,99</t>
+          <t>42,01; 92,46</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,94; 74,44</t>
+          <t>57,13; 74,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66,64; 86,11</t>
+          <t>60,31; 83,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62,71; 76,34</t>
+          <t>60,7; 74,51</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>19534</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9025; 16542</t>
+          <t>9657; 17889</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2976; 6228</t>
+          <t>2780; 6478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13854; 22488</t>
+          <t>14117; 23426</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>17396</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3417; 10366</t>
+          <t>3871; 11517</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6336; 11006</t>
+          <t>6358; 12105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11297; 20283</t>
+          <t>11983; 22168</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>27495</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18182; 26865</t>
+          <t>19442; 29087</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2198</t>
+          <t>540; 3547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18792; 28068</t>
+          <t>21682; 31693</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>40799</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20476; 32310</t>
+          <t>22176; 34512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5111; 10023</t>
+          <t>8152; 13993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27645; 41061</t>
+          <t>33055; 47012</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>28574</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11796; 25142</t>
+          <t>15008; 31407</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2345; 6950</t>
+          <t>2670; 7213</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16657; 30104</t>
+          <t>20959; 36946</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>14629</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6637</t>
+          <t>0; 6084</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5565; 12072</t>
+          <t>5815; 13550</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8251; 17585</t>
+          <t>8249; 18153</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>103595</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>39372</t>
+          <t>44832</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132864</t>
+          <t>148427</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80012; 104592</t>
+          <t>90089; 116823</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33872; 43767</t>
+          <t>36329; 50252</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119980; 146072</t>
+          <t>132289; 162388</t>
         </is>
       </c>
     </row>
